--- a/data/TTC/最新版班表/2026-10/TTC_TA.xlsx
+++ b/data/TTC/最新版班表/2026-10/TTC_TA.xlsx
@@ -956,12 +956,9 @@
 8:36</t>
         </is>
       </c>
-      <c r="O7" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr">
@@ -1006,12 +1003,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="V7" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="W7" s="1" t="inlineStr">
@@ -1279,12 +1273,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="AD8" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
     </row>
@@ -1438,12 +1429,9 @@
 8:54</t>
         </is>
       </c>
-      <c r="W9" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="X9" s="1" t="inlineStr">
@@ -1484,12 +1472,9 @@
 8:38</t>
         </is>
       </c>
-      <c r="AC9" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -1641,12 +1626,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="V10" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="W10" s="1" t="inlineStr">
@@ -1817,12 +1799,9 @@
 8:08</t>
         </is>
       </c>
-      <c r="Q11" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -2057,12 +2036,9 @@
 9:05</t>
         </is>
       </c>
-      <c r="U12" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-WRSL
-17:30
-8:00</t>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>WRSL</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -2205,12 +2181,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="L13" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="M13" s="1" t="inlineStr">
@@ -2537,12 +2510,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="AC14" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-WRSL
-17:30
-8:00</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>WRSL</t>
         </is>
       </c>
       <c r="AD14" s="1" t="inlineStr">
@@ -2573,12 +2543,9 @@
 9:17</t>
         </is>
       </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
@@ -2775,36 +2742,24 @@
           <t>陳孟柔</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2981,36 +2936,24 @@
           <t>張雅涵</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3041,12 +2984,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="L17" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="M17" s="1" t="inlineStr">
@@ -3091,12 +3031,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="S17" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="T17" s="1" t="inlineStr">
@@ -3334,12 +3271,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="W18" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -3352,12 +3286,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="Z18" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AA18" s="1" t="inlineStr">
@@ -3435,12 +3366,9 @@
 8:05</t>
         </is>
       </c>
-      <c r="H19" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="I19" s="1" t="inlineStr">
@@ -3502,20 +3430,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q19" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="R19" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -3533,20 +3455,14 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="V19" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="W19" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -3583,12 +3499,9 @@
 8:15</t>
         </is>
       </c>
-      <c r="AC19" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -3608,36 +3521,24 @@
           <t>陳婉禎</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3823,12 +3724,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3948,12 +3846,9 @@
 9:00</t>
         </is>
       </c>
-      <c r="U21" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-WRSL
-17:30
-8:00</t>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>WRSL</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -4289,12 +4184,9 @@
 DO2</t>
         </is>
       </c>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="K23" s="1" t="inlineStr">
@@ -4305,12 +4197,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="L23" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="M23" s="1" t="inlineStr">
@@ -4427,12 +4316,9 @@
 8:16</t>
         </is>
       </c>
-      <c r="AC23" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-WRSL
-17:30
-8:00</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>WRSL</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -4452,28 +4338,19 @@
           <t>陳韋汝</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5050,12 +4927,9 @@
 8:21</t>
         </is>
       </c>
-      <c r="AB26" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AC26" s="1" t="inlineStr">
@@ -5483,12 +5357,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="AC28" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AD28" s="1" t="inlineStr">
@@ -5545,12 +5416,9 @@
 9:18</t>
         </is>
       </c>
-      <c r="H29" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="I29" s="1" t="inlineStr">
@@ -5692,12 +5560,9 @@
 9:00</t>
         </is>
       </c>
-      <c r="AB29" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUTS
-17:30
-8:00</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>LUTS</t>
         </is>
       </c>
       <c r="AC29" s="1" t="inlineStr">
@@ -6044,12 +5909,9 @@
 8:10</t>
         </is>
       </c>
-      <c r="S31" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -6250,12 +6112,9 @@
 8:29</t>
         </is>
       </c>
-      <c r="R32" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUTS
-17:30
-8:00</t>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>LUTS</t>
         </is>
       </c>
       <c r="S32" s="1" t="inlineStr">
@@ -6355,12 +6214,9 @@
           <t>賴世強</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-CMP
-17:30
-8:00</t>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CMP</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
@@ -6448,20 +6304,14 @@
 8:18</t>
         </is>
       </c>
-      <c r="P33" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-CMP
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="Q33" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-CMP
-17:30
-8:00</t>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>CMP</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>CMP</t>
         </is>
       </c>
       <c r="R33" s="1" t="inlineStr">
@@ -7375,20 +7225,14 @@
 8:02</t>
         </is>
       </c>
-      <c r="AC37" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-FAC
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AD37" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>FAC</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
     </row>
@@ -7489,28 +7333,19 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="P38" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="Q38" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="R38" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -8094,20 +7929,14 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="L41" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="M41" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -8508,12 +8337,9 @@
 8:16</t>
         </is>
       </c>
-      <c r="L43" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="M43" s="1" t="inlineStr">
@@ -8537,20 +8363,14 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="P43" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="Q43" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -8558,20 +8378,14 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="S43" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="T43" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -8579,12 +8393,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="V43" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -8807,20 +8618,14 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="Y44" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="Z44" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -9263,12 +9068,9 @@
 8:02</t>
         </is>
       </c>
-      <c r="AC46" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
@@ -9288,12 +9090,9 @@
           <t>陳湘晴</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-CMP
-17:30
-8:00</t>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CMP</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
@@ -9336,12 +9135,9 @@
 DO2</t>
         </is>
       </c>
-      <c r="J47" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-CMP
-17:30
-8:00</t>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>CMP</t>
         </is>
       </c>
       <c r="K47" s="1" t="inlineStr">
@@ -9378,20 +9174,14 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="P47" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="Q47" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="R47" s="1" t="inlineStr">
@@ -9402,12 +9192,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="S47" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="T47" s="1" t="inlineStr">
@@ -9517,12 +9304,9 @@
 9:00</t>
         </is>
       </c>
-      <c r="F48" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -9530,12 +9314,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="H48" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-FAC
-17:30
-8:00</t>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>FAC</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -9548,12 +9329,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -9967,12 +9745,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="J50" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -10059,12 +9834,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="W50" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="X50" s="1" t="inlineStr">
@@ -10523,12 +10295,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="AD52" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
     </row>
@@ -10599,12 +10368,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>8:00
-DTT1
-17:00
-8:00</t>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>DTT1</t>
         </is>
       </c>
       <c r="L53" s="1" t="inlineStr">
@@ -11145,20 +10911,14 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="AB55" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AC55" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
@@ -11388,12 +11148,9 @@
           <t>賴玟羽</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-CMP
-17:30
-8:00</t>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>CMP</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11581,12 +11338,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="AD57" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
     </row>
@@ -12108,20 +11862,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="N60" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="O60" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -12129,12 +11877,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="Q60" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="R60" s="1" t="inlineStr">
@@ -12145,12 +11890,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="S60" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -12351,12 +12093,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="R61" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUTS
-17:30
-8:00</t>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>LUTS</t>
         </is>
       </c>
       <c r="S61" s="1" t="inlineStr">
@@ -12767,12 +12506,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q63" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -13091,20 +12827,14 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="E65" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -13726,12 +13456,9 @@
 8:01</t>
         </is>
       </c>
-      <c r="D68" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -13744,12 +13471,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="G68" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -13996,12 +13720,9 @@
 8:16</t>
         </is>
       </c>
-      <c r="L69" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -14035,12 +13756,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="R69" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -14578,20 +14296,14 @@
 8:39</t>
         </is>
       </c>
-      <c r="E72" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="F72" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -14781,12 +14493,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr">
@@ -15092,12 +14801,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="R74" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUTS
-17:30
-8:00</t>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>LUTS</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -15126,12 +14832,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="W74" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
@@ -15307,12 +15010,9 @@
 8:10</t>
         </is>
       </c>
-      <c r="S75" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="T75" s="1" t="inlineStr">
@@ -17014,12 +16714,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="S83" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="T83" s="1" t="inlineStr">
